--- a/it_forms/007_fasta_file_analysis_submission--it_forms.xlsx
+++ b/it_forms/007_fasta_file_analysis_submission--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1031,8 +1031,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'alignment'}</t>
+          <t>alignment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Alignment'}</t>
+          <t>Alignment</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'gene_prediction'}</t>
+          <t>gene_prediction</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Gene prediction'}</t>
+          <t>Gene prediction</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'gene_prediction_and_annotation'}</t>
+          <t>gene_prediction_and_annotation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Gene prediction and annotation'}</t>
+          <t>Gene prediction and annotation</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'genomic_dna'}</t>
+          <t>genomic_dna</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Genomic DNA'}</t>
+          <t>Genomic DNA</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'genomic_rna'}</t>
+          <t>genomic_rna</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Genomic RNA'}</t>
+          <t>Genomic RNA</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'metagenomic_dna'}</t>
+          <t>metagenomic_dna</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Metagenomic DNA'}</t>
+          <t>Metagenomic DNA</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'metagenomic_rna'}</t>
+          <t>metagenomic_rna</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Metagenomic RNA'}</t>
+          <t>Metagenomic RNA</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'human'}</t>
+          <t>human</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Human'}</t>
+          <t>Human</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'mouse'}</t>
+          <t>mouse</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Mouse'}</t>
+          <t>Mouse</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'zebrafish'}</t>
+          <t>zebrafish</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Zebrafish'}</t>
+          <t>Zebrafish</t>
         </is>
       </c>
     </row>
